--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488246_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488246_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.4451</v>
+        <v>8.2492</v>
       </c>
       <c r="E2" t="n">
-        <v>7.5871</v>
+        <v>7.3913</v>
       </c>
       <c r="F2" t="n">
         <v>0.8579</v>
@@ -610,10 +610,10 @@
         <v>2.0382</v>
       </c>
       <c r="S2" t="n">
-        <v>0.9476</v>
+        <v>0.7517</v>
       </c>
       <c r="T2" t="n">
-        <v>0.7796999999999999</v>
+        <v>0.5839</v>
       </c>
       <c r="U2" t="n">
         <v>0.1679</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>7.96</v>
+        <v>7.3762</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9346</v>
+        <v>3.6955</v>
       </c>
       <c r="F3" t="n">
-        <v>4.0254</v>
+        <v>3.6807</v>
       </c>
       <c r="G3" t="n">
         <v>4.2753</v>
@@ -688,13 +688,13 @@
         <v>1.6676</v>
       </c>
       <c r="S3" t="n">
-        <v>1.7026</v>
+        <v>1.1189</v>
       </c>
       <c r="T3" t="n">
-        <v>0.9439</v>
+        <v>0.7048</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7588</v>
+        <v>0.4141</v>
       </c>
       <c r="V3" t="n">
         <v>0.3144</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>6.7785</v>
+        <v>7.2999</v>
       </c>
       <c r="E4" t="n">
-        <v>3.9507</v>
+        <v>4.2012</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8279</v>
+        <v>3.0987</v>
       </c>
       <c r="G4" t="n">
         <v>6.0012</v>
@@ -766,13 +766,13 @@
         <v>1.297</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.6137</v>
       </c>
       <c r="T4" t="n">
-        <v>0.291</v>
+        <v>0.5416</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1987</v>
+        <v>0.0721</v>
       </c>
       <c r="V4" t="n">
         <v>0.3144</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6881</v>
+        <v>7.082</v>
       </c>
       <c r="E5" t="n">
         <v>5.3124</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3757</v>
+        <v>1.7696</v>
       </c>
       <c r="G5" t="n">
         <v>6.2314</v>
@@ -844,13 +844,13 @@
         <v>2.0382</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6551</v>
+        <v>-0.2611</v>
       </c>
       <c r="T5" t="n">
         <v>0.1269</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7819</v>
+        <v>-0.388</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>6.0885</v>
+        <v>6.2646</v>
       </c>
       <c r="E6" t="n">
-        <v>4.3666</v>
+        <v>4.7151</v>
       </c>
       <c r="F6" t="n">
-        <v>1.7219</v>
+        <v>1.5495</v>
       </c>
       <c r="G6" t="n">
         <v>2.5109</v>
@@ -922,13 +922,13 @@
         <v>2.4087</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8364</v>
+        <v>1.0125</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2363</v>
+        <v>0.5848</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6001</v>
+        <v>0.4278</v>
       </c>
       <c r="V6" t="n">
         <v>1.2589</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>5.1088</v>
+        <v>4.0359</v>
       </c>
       <c r="E7" t="n">
-        <v>3.9993</v>
+        <v>3.1726</v>
       </c>
       <c r="F7" t="n">
-        <v>1.1095</v>
+        <v>0.8633</v>
       </c>
       <c r="G7" t="n">
         <v>4.9979</v>
@@ -1000,13 +1000,13 @@
         <v>1.8529</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2782</v>
+        <v>1.2053</v>
       </c>
       <c r="T7" t="n">
-        <v>1.7273</v>
+        <v>0.9006</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5508999999999999</v>
+        <v>0.3046</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3144</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.8888</v>
+        <v>3.8025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4877</v>
+        <v>1.0321</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4011</v>
+        <v>2.7704</v>
       </c>
       <c r="G8" t="n">
         <v>2.005</v>
@@ -1078,13 +1078,13 @@
         <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.6715</v>
+        <v>0.2422</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3954</v>
+        <v>0.1489</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2761</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V8" t="n">
         <v>0.6289</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. PARRA RIVERA</t>
+          <t>J. SANCHEZ BARQUIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>2.7201</v>
+        <v>3.4347</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6149</v>
+        <v>2.2609</v>
       </c>
       <c r="F9" t="n">
-        <v>2.1052</v>
+        <v>1.1738</v>
       </c>
       <c r="G9" t="n">
-        <v>1.9317</v>
+        <v>2.1252</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5169</v>
+        <v>3.3217</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4147</v>
+        <v>-1.1965</v>
       </c>
       <c r="J9" t="n">
-        <v>1.0609</v>
+        <v>2.8205</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5372</v>
+        <v>2.7269</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.4763</v>
+        <v>0.0936</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8707</v>
+        <v>-0.6952</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.0203</v>
+        <v>0.5949</v>
       </c>
       <c r="O9" t="n">
-        <v>0.891</v>
+        <v>-1.2901</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1.1117</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.8529</v>
+        <v>-0.9264</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7879</v>
+        <v>0.1977</v>
       </c>
       <c r="T9" t="n">
-        <v>0.148</v>
+        <v>0.3669</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6399</v>
+        <v>-0.1691</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0005</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.2583</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SANCHEZ BARQUIN</t>
+          <t>A. PARRA RIVERA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>2.3995</v>
+        <v>2.1352</v>
       </c>
       <c r="E10" t="n">
-        <v>1.4228</v>
+        <v>0.5717</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9768</v>
+        <v>1.5635</v>
       </c>
       <c r="G10" t="n">
-        <v>2.1252</v>
+        <v>1.9317</v>
       </c>
       <c r="H10" t="n">
-        <v>3.3217</v>
+        <v>1.5169</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.1965</v>
+        <v>0.4147</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8205</v>
+        <v>1.0609</v>
       </c>
       <c r="K10" t="n">
-        <v>2.7269</v>
+        <v>1.5372</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0936</v>
+        <v>-0.4763</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6952</v>
+        <v>0.8707</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5949</v>
+        <v>-0.0203</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.2901</v>
+        <v>0.891</v>
       </c>
       <c r="P10" t="n">
-        <v>1.1117</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0382</v>
+        <v>1.8529</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8374</v>
+        <v>0.203</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4713</v>
+        <v>0.1048</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3661</v>
+        <v>0.0982</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.0005</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2583</v>
       </c>
     </row>
     <row r="11">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0.5152</v>
+        <v>0.3242</v>
       </c>
       <c r="E12" t="n">
-        <v>2.7474</v>
+        <v>2.7042</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.2323</v>
+        <v>-2.38</v>
       </c>
       <c r="G12" t="n">
         <v>-0.2117</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5034</v>
+        <v>0.3124</v>
       </c>
       <c r="T12" t="n">
-        <v>0.291</v>
+        <v>0.2478</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2124</v>
+        <v>0.0646</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2589</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.3491</v>
+        <v>-0.4158</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.6456</v>
+        <v>-0.8846000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.2965</v>
+        <v>0.4688</v>
       </c>
       <c r="G13" t="n">
         <v>-0.195</v>
@@ -1468,13 +1468,13 @@
         <v>0.7411</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3636</v>
+        <v>0.2969</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5099</v>
+        <v>0.2708</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1462</v>
+        <v>0.0261</v>
       </c>
       <c r="V13" t="n">
         <v>-1.2589</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.081</v>
+        <v>-0.8791</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.3014</v>
+        <v>-0.1488</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7796</v>
+        <v>-0.7302999999999999</v>
       </c>
       <c r="G14" t="n">
         <v>-0.0067</v>
@@ -1546,13 +1546,13 @@
         <v>0.1853</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0007</v>
+        <v>0.2011</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.0336</v>
+        <v>0.1191</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2589</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>49.12869999999999</v>
+        <v>49.6757</v>
       </c>
       <c r="E15" t="n">
-        <v>34.44269999999999</v>
+        <v>34.9898</v>
       </c>
       <c r="F15" t="n">
-        <v>14.686</v>
+        <v>14.6859</v>
       </c>
       <c r="G15" t="n">
         <v>35.1469</v>
@@ -1606,16 +1606,16 @@
         <v>9.751899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>0.6451999999999998</v>
+        <v>0.6452</v>
       </c>
       <c r="N15" t="n">
-        <v>2.6409</v>
+        <v>2.640899999999999</v>
       </c>
       <c r="O15" t="n">
         <v>-1.9956</v>
       </c>
       <c r="P15" t="n">
-        <v>9.264299999999999</v>
+        <v>9.2643</v>
       </c>
       <c r="Q15" t="n">
         <v>-10.1906</v>
@@ -1624,19 +1624,19 @@
         <v>19.4553</v>
       </c>
       <c r="S15" t="n">
-        <v>5.347300000000001</v>
+        <v>5.894300000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>4.1537</v>
+        <v>4.700900000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1938</v>
+        <v>1.1937</v>
       </c>
       <c r="V15" t="n">
         <v>-0.6300999999999999</v>
       </c>
       <c r="W15" t="n">
-        <v>5.9783</v>
+        <v>5.978299999999999</v>
       </c>
       <c r="X15" t="n">
         <v>-6.608199999999999</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.3275</v>
+        <v>1.9524</v>
       </c>
       <c r="E16" t="n">
-        <v>6.325</v>
+        <v>5.6395</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.9975</v>
+        <v>-3.6872</v>
       </c>
       <c r="G16" t="n">
         <v>2.8965</v>
@@ -1702,13 +1702,13 @@
         <v>1.6676</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1985</v>
+        <v>-0.5736</v>
       </c>
       <c r="T16" t="n">
-        <v>0.6579</v>
+        <v>-0.0276</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.8563</v>
+        <v>-0.5459000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2257</v>
+        <v>-0.948</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8334</v>
+        <v>0.9314</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.0591</v>
+        <v>-1.8793</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3657</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.6747</v>
+        <v>-0.397</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.383</v>
+        <v>-0.2851</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2917</v>
+        <v>-0.1119</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.9083</v>
+        <v>-1.7611</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.7434</v>
+        <v>-1.6455</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1649</v>
+        <v>-0.1156</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9053</v>
@@ -1858,13 +1858,13 @@
         <v>0.1853</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2619</v>
+        <v>-0.1147</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1641</v>
+        <v>-0.06619999999999999</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0977</v>
+        <v>-0.0485</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9989</v>
+        <v>-2.2777</v>
       </c>
       <c r="E19" t="n">
-        <v>0.4489</v>
+        <v>0.1551</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.4478</v>
+        <v>-2.4329</v>
       </c>
       <c r="G19" t="n">
         <v>-2.7313</v>
@@ -1936,13 +1936,13 @@
         <v>0.9264</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.194</v>
+        <v>-0.4729</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1816</v>
+        <v>-0.1122</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3756</v>
+        <v>-0.3606</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.0133</v>
+        <v>-2.8008</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7955</v>
+        <v>-0.8935</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2177</v>
+        <v>-1.9073</v>
       </c>
       <c r="G20" t="n">
         <v>-3.5887</v>
@@ -2014,13 +2014,13 @@
         <v>0.7411</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.4807</v>
+        <v>-0.2683</v>
       </c>
       <c r="T20" t="n">
-        <v>0.2027</v>
+        <v>0.1048</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6835</v>
+        <v>-0.3731</v>
       </c>
       <c r="V20" t="n">
         <v>0.315</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2588</v>
+        <v>-3.871</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7989</v>
+        <v>0.8196</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.0577</v>
+        <v>-4.6906</v>
       </c>
       <c r="G21" t="n">
         <v>-2.3768</v>
@@ -2092,13 +2092,13 @@
         <v>0.9264</v>
       </c>
       <c r="S21" t="n">
-        <v>0.9523</v>
+        <v>0.3401</v>
       </c>
       <c r="T21" t="n">
-        <v>1.399</v>
+        <v>0.4197</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4467</v>
+        <v>-0.0796</v>
       </c>
       <c r="V21" t="n">
         <v>0.945</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9307</v>
+        <v>-4.7354</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9142</v>
+        <v>-1.6205</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.0165</v>
+        <v>-3.115</v>
       </c>
       <c r="G22" t="n">
         <v>-2.6798</v>
@@ -2170,13 +2170,13 @@
         <v>0.9264</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.8068</v>
+        <v>-0.6115</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5596</v>
+        <v>-0.2658</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2472</v>
+        <v>-0.3457</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2589</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6334</v>
+        <v>-5.0126</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.4365</v>
+        <v>-3.0448</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.1969</v>
+        <v>-1.9678</v>
       </c>
       <c r="G23" t="n">
         <v>-4.1417</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6208</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3619</v>
+        <v>0.0299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2589</v>
+        <v>-0.0299</v>
       </c>
       <c r="V23" t="n">
         <v>-0.315</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-6.7111</v>
+        <v>-5.9362</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.5483</v>
+        <v>-1.9607</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.1628</v>
+        <v>-3.9755</v>
       </c>
       <c r="G24" t="n">
         <v>-5.2145</v>
@@ -2326,13 +2326,13 @@
         <v>0.5558999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.6262</v>
+        <v>0.1486</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5931</v>
+        <v>-0.0056</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0331</v>
+        <v>0.1542</v>
       </c>
       <c r="V24" t="n">
         <v>-0.3144</v>
@@ -2347,7 +2347,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>P. GOMEZ MORENO</t>
+          <t>J. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,73 +2359,73 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-7.3468</v>
+        <v>-6.8313</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.7877</v>
+        <v>-3.8461</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.5591</v>
+        <v>-2.9852</v>
       </c>
       <c r="G25" t="n">
-        <v>-7.5219</v>
+        <v>-2.9077</v>
       </c>
       <c r="H25" t="n">
-        <v>-6.1612</v>
+        <v>-2.6067</v>
       </c>
       <c r="I25" t="n">
-        <v>-1.3608</v>
+        <v>-0.301</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.641</v>
+        <v>0.8633999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-3.7239</v>
+        <v>0.8112</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0829</v>
+        <v>0.0522</v>
       </c>
       <c r="M25" t="n">
-        <v>-3.881</v>
+        <v>-3.7711</v>
       </c>
       <c r="N25" t="n">
-        <v>-2.4373</v>
+        <v>-3.418</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.4437</v>
+        <v>-0.3531</v>
       </c>
       <c r="P25" t="n">
-        <v>0.5558999999999999</v>
+        <v>-4.6322</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.1853</v>
+        <v>-5.7439</v>
       </c>
       <c r="R25" t="n">
-        <v>0.7411</v>
+        <v>1.1117</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2487</v>
+        <v>-0.5503</v>
       </c>
       <c r="T25" t="n">
-        <v>0.0386</v>
+        <v>-0.2244</v>
       </c>
       <c r="U25" t="n">
-        <v>0.2101</v>
+        <v>-0.3258</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.6294</v>
+        <v>1.2589</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.2589</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>J. LATORRE SANCHEZ</t>
+          <t>P. GOMEZ MORENO</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-7.6726</v>
+        <v>-7.4121</v>
       </c>
       <c r="E26" t="n">
-        <v>-4.4337</v>
+        <v>-3.9836</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2389</v>
+        <v>-3.4285</v>
       </c>
       <c r="G26" t="n">
-        <v>-2.9077</v>
+        <v>-7.5219</v>
       </c>
       <c r="H26" t="n">
-        <v>-2.6067</v>
+        <v>-6.1612</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.301</v>
+        <v>-1.3608</v>
       </c>
       <c r="J26" t="n">
-        <v>0.8633999999999999</v>
+        <v>-3.641</v>
       </c>
       <c r="K26" t="n">
-        <v>0.8112</v>
+        <v>-3.7239</v>
       </c>
       <c r="L26" t="n">
-        <v>0.0522</v>
+        <v>0.0829</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.7711</v>
+        <v>-3.881</v>
       </c>
       <c r="N26" t="n">
-        <v>-3.418</v>
+        <v>-2.4373</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.3531</v>
+        <v>-1.4437</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.6322</v>
+        <v>0.5558999999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-5.7439</v>
+        <v>-0.1853</v>
       </c>
       <c r="R26" t="n">
-        <v>1.1117</v>
+        <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.3915</v>
+        <v>0.1834</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.8120000000000001</v>
+        <v>-0.1573</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.5795</v>
+        <v>0.3407</v>
       </c>
       <c r="V26" t="n">
-        <v>1.2589</v>
+        <v>-0.6294</v>
       </c>
       <c r="W26" t="n">
-        <v>1.2589</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="27">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-7.7566</v>
+        <v>-7.5361</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.4327</v>
+        <v>-5.2369</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.3238</v>
+        <v>-2.2992</v>
       </c>
       <c r="G27" t="n">
         <v>-5.6101</v>
@@ -2560,13 +2560,13 @@
         <v>1.297</v>
       </c>
       <c r="S27" t="n">
-        <v>-1.293</v>
+        <v>-1.0725</v>
       </c>
       <c r="T27" t="n">
-        <v>-0.7996</v>
+        <v>-0.6037</v>
       </c>
       <c r="U27" t="n">
-        <v>-0.4934</v>
+        <v>-0.4688</v>
       </c>
       <c r="V27" t="n">
         <v>0.6289</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-49.1287</v>
+        <v>-47.16990000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>-14.6858</v>
+        <v>-14.686</v>
       </c>
       <c r="F28" t="n">
-        <v>-34.44269999999999</v>
+        <v>-32.48410000000001</v>
       </c>
       <c r="G28" t="n">
         <v>-35.147</v>
@@ -2611,10 +2611,10 @@
         <v>-7.7563</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.6452</v>
+        <v>-0.6451999999999996</v>
       </c>
       <c r="K28" t="n">
-        <v>-2.6409</v>
+        <v>-2.640899999999999</v>
       </c>
       <c r="L28" t="n">
         <v>1.995700000000001</v>
@@ -2638,13 +2638,13 @@
         <v>10.1906</v>
       </c>
       <c r="S28" t="n">
-        <v>-5.3471</v>
+        <v>-3.3887</v>
       </c>
       <c r="T28" t="n">
         <v>-1.1935</v>
       </c>
       <c r="U28" t="n">
-        <v>-4.1535</v>
+        <v>-2.1949</v>
       </c>
       <c r="V28" t="n">
         <v>0.6301000000000001</v>
